--- a/resources/templates/standard/A5100-01.xlsx
+++ b/resources/templates/standard/A5100-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>내부심사 년간 계획서 및 실적</t>
   </si>
@@ -848,12 +851,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -890,17 +895,17 @@
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO1" s="3"/>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR1" s="3"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU1" s="3"/>
       <c r="AV1" s="3"/>
@@ -1143,12 +1148,12 @@
       <c r="AI6" s="8"/>
       <c r="AJ6" s="8"/>
       <c r="AK6" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL6" s="9"/>
       <c r="AM6" s="9"/>
       <c r="AN6" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO6" s="10"/>
       <c r="AP6" s="10"/>
@@ -1161,7 +1166,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1199,12 +1204,12 @@
       <c r="AI7" s="11"/>
       <c r="AJ7" s="11"/>
       <c r="AK7" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL7" s="9"/>
       <c r="AM7" s="9"/>
       <c r="AN7" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO7" s="10"/>
       <c r="AP7" s="10"/>
@@ -1217,11 +1222,11 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
@@ -1231,7 +1236,7 @@
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
       <c r="K8" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L8" s="13"/>
       <c r="M8" s="13"/>
@@ -1261,12 +1266,12 @@
       <c r="AK8" s="13"/>
       <c r="AL8" s="13"/>
       <c r="AM8" s="15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN8" s="15"/>
       <c r="AO8" s="15"/>
       <c r="AP8" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
@@ -1341,51 +1346,51 @@
       <c r="M10" s="13"/>
       <c r="N10" s="13"/>
       <c r="O10" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P10" s="16"/>
       <c r="Q10" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R10" s="16"/>
       <c r="S10" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T10" s="16"/>
       <c r="U10" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V10" s="16"/>
       <c r="W10" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X10" s="16"/>
       <c r="Y10" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AB10" s="16"/>
       <c r="AC10" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD10" s="16"/>
       <c r="AE10" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF10" s="16"/>
       <c r="AG10" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH10" s="16"/>
       <c r="AI10" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ10" s="16"/>
       <c r="AK10" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" s="16"/>
       <c r="AM10" s="15"/>
@@ -1455,7 +1460,7 @@
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
@@ -1465,7 +1470,7 @@
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
       <c r="K12" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
@@ -1495,7 +1500,7 @@
       <c r="AK12" s="23"/>
       <c r="AL12" s="23"/>
       <c r="AM12" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN12" s="24"/>
       <c r="AO12" s="24"/>
@@ -1561,7 +1566,7 @@
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
       <c r="C14" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
@@ -1715,19 +1720,19 @@
       </c>
       <c r="B17" s="27"/>
       <c r="C17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
       <c r="F17" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" s="29"/>
       <c r="H17" s="29"/>
       <c r="I17" s="29"/>
       <c r="J17" s="29"/>
       <c r="K17" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L17" s="19"/>
       <c r="M17" s="19"/>
@@ -1824,14 +1829,14 @@
       <c r="D19" s="28"/>
       <c r="E19" s="28"/>
       <c r="F19" s="29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" s="29"/>
       <c r="H19" s="29"/>
       <c r="I19" s="29"/>
       <c r="J19" s="29"/>
       <c r="K19" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
@@ -1928,14 +1933,14 @@
       <c r="D21" s="28"/>
       <c r="E21" s="28"/>
       <c r="F21" s="29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" s="29"/>
       <c r="H21" s="29"/>
       <c r="I21" s="29"/>
       <c r="J21" s="29"/>
       <c r="K21" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L21" s="19"/>
       <c r="M21" s="19"/>
@@ -2032,14 +2037,14 @@
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
       <c r="F23" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G23" s="29"/>
       <c r="H23" s="29"/>
       <c r="I23" s="29"/>
       <c r="J23" s="29"/>
       <c r="K23" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L23" s="19"/>
       <c r="M23" s="19"/>
@@ -2136,14 +2141,14 @@
       <c r="D25" s="28"/>
       <c r="E25" s="28"/>
       <c r="F25" s="29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G25" s="29"/>
       <c r="H25" s="29"/>
       <c r="I25" s="29"/>
       <c r="J25" s="29"/>
       <c r="K25" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L25" s="19"/>
       <c r="M25" s="19"/>
@@ -2240,14 +2245,14 @@
       <c r="D27" s="28"/>
       <c r="E27" s="28"/>
       <c r="F27" s="29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G27" s="29"/>
       <c r="H27" s="29"/>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
       <c r="K27" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
@@ -2344,14 +2349,14 @@
       <c r="D29" s="28"/>
       <c r="E29" s="28"/>
       <c r="F29" s="29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G29" s="29"/>
       <c r="H29" s="29"/>
       <c r="I29" s="29"/>
       <c r="J29" s="29"/>
       <c r="K29" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L29" s="19"/>
       <c r="M29" s="19"/>
@@ -2448,14 +2453,14 @@
       <c r="D31" s="28"/>
       <c r="E31" s="28"/>
       <c r="F31" s="29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G31" s="29"/>
       <c r="H31" s="29"/>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
       <c r="K31" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L31" s="19"/>
       <c r="M31" s="19"/>
@@ -2552,14 +2557,14 @@
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
       <c r="F33" s="29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G33" s="29"/>
       <c r="H33" s="29"/>
       <c r="I33" s="29"/>
       <c r="J33" s="29"/>
       <c r="K33" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L33" s="19"/>
       <c r="M33" s="19"/>
@@ -2655,7 +2660,7 @@
       </c>
       <c r="B35" s="17"/>
       <c r="C35" s="35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D35" s="35"/>
       <c r="E35" s="35"/>
@@ -2669,43 +2674,43 @@
       <c r="M35" s="35"/>
       <c r="N35" s="35"/>
       <c r="O35" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P35" s="20"/>
       <c r="Q35" s="36"/>
       <c r="R35" s="36"/>
       <c r="S35" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T35" s="22"/>
       <c r="U35" s="22"/>
       <c r="V35" s="22"/>
       <c r="W35" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X35" s="20"/>
       <c r="Y35" s="36"/>
       <c r="Z35" s="36"/>
       <c r="AA35" s="22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AB35" s="22"/>
       <c r="AC35" s="22"/>
       <c r="AD35" s="22"/>
       <c r="AE35" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF35" s="20"/>
       <c r="AG35" s="36"/>
       <c r="AH35" s="36"/>
       <c r="AI35" s="22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AJ35" s="22"/>
       <c r="AK35" s="22"/>
       <c r="AL35" s="22"/>
       <c r="AM35" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN35" s="24"/>
       <c r="AO35" s="24"/>
@@ -2771,7 +2776,7 @@
       <c r="A37" s="17"/>
       <c r="B37" s="17"/>
       <c r="C37" s="26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D37" s="26"/>
       <c r="E37" s="26"/>
